--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mobilità sostenibile.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Mobilità sostenibile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="115">
   <si>
     <r>
       <t xml:space="preserve">
@@ -570,7 +570,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -890,10 +890,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Presenta richiesta</t>
+    <t>Invia richiesta</t>
   </si>
   <si>
-    <t>Aggiungi i documenti</t>
+    <t>Aggiungi documenti</t>
   </si>
   <si>
     <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
@@ -916,7 +916,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -999,18 +999,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -1914,7 +1902,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>59</v>
@@ -1926,13 +1914,13 @@
         <v>59</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
